--- a/outputs/188-39.xlsx
+++ b/outputs/188-39.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="56">
   <si>
     <t xml:space="preserve">Location</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t xml:space="preserve">harigu.p@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
   </si>
 </sst>
 </file>
@@ -281,27 +284,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -763,187 +766,154 @@
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A2,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A2,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A2,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="C2" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A2,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A2,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A2,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="D2" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A2,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A2,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A2,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>N/A</v>
+      <c r="B2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A3,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A3,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A3,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>Branch Manager</v>
-      </c>
-      <c r="C3" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A3,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A3,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A3,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
-        <v>7768825777</v>
-      </c>
-      <c r="D3" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A3,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A3,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A3,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>vidhyan@gmail.com</v>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A4,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A4,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A4,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>Branch Credit Manager</v>
-      </c>
-      <c r="C4" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A4,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A4,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A4,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
-        <v>9592887766</v>
-      </c>
-      <c r="D4" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A4,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A4,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A4,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>priyapatil.k@gmail.com</v>
+      <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A5,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A5,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A5,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="C5" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A5,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A5,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A5,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="D5" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A5,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A5,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A5,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>N/A</v>
+      <c r="B5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A6,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A6,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A6,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="C6" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A6,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A6,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A6,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="D6" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A6,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A6,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A6,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>N/A</v>
+      <c r="B6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A7,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A7,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A7,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>Branch Manager</v>
+      <c r="B7" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="n">
-        <f aca="false">IF(OR(VLOOKUP(A7,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A7,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A7,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
         <v>9999143233</v>
       </c>
-      <c r="D7" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A7,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A7,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A7,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>vivekgovekar1@gmail.com</v>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A8,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A8,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A8,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>Branch Manager</v>
-      </c>
-      <c r="C8" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A8,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A8,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A8,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
-        <v>9425493385</v>
-      </c>
-      <c r="D8" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A8,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A8,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A8,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>nagarajup@yahoo.com</v>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A9,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A9,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A9,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="C9" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A9,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A9,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A9,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="D9" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A9,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A9,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A9,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>N/A</v>
+      <c r="B9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A10,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A10,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A10,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>Branch Credit Manager</v>
-      </c>
-      <c r="C10" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A10,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A10,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A10,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
-        <v>9845267900</v>
-      </c>
-      <c r="D10" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A10,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A10,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A10,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>krishnap@gmail.com</v>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A11,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A11,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A11,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="C11" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A11,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A11,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A11,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
-        <v>N/A</v>
-      </c>
-      <c r="D11" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A11,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A11,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A11,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>N/A</v>
+      <c r="B11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A12,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A12,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A12,'main sheet'!$A$2:$E$12,5,FALSE()),"N/A")</f>
-        <v>Branch Credit Manager</v>
-      </c>
-      <c r="C12" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A12,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A12,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A12,'main sheet'!$A$2:$E$12,3,FALSE()),"N/A")</f>
-        <v>7522944799</v>
-      </c>
-      <c r="D12" s="4" t="str">
-        <f aca="false">IF(OR(VLOOKUP(A12,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Manager",VLOOKUP(A12,'main sheet'!$A$2:$E$12,5,FALSE())="Branch Credit Manager"),VLOOKUP(A12,'main sheet'!$A$2:$E$12,4,FALSE()),"N/A")</f>
-        <v>harigu.p@gmail.com</v>
+      <c r="B12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/188-39.xlsx
+++ b/outputs/188-39.xlsx
@@ -507,7 +507,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.54"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" s="2" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -524,7 +524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -541,7 +541,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -558,7 +558,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
@@ -575,7 +575,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
@@ -592,7 +592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
@@ -609,7 +609,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
@@ -626,7 +626,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
@@ -643,7 +643,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
@@ -660,7 +660,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>42</v>
       </c>
@@ -677,7 +677,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>46</v>
       </c>
@@ -694,7 +694,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>51</v>
       </c>
@@ -748,7 +748,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36.84"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -762,7 +762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -776,12 +776,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>12</v>
@@ -790,12 +790,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>17</v>
@@ -804,7 +804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
@@ -818,7 +818,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>25</v>
       </c>
@@ -832,12 +832,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>9999143233</v>
@@ -846,12 +846,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>35</v>
@@ -860,7 +860,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>37</v>
       </c>
@@ -874,12 +874,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>44</v>
@@ -888,7 +888,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>46</v>
       </c>
@@ -902,12 +902,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>53</v>
